--- a/artfynd/A 38978-2023 artfynd.xlsx
+++ b/artfynd/A 38978-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122640518</v>
+        <v>122640499</v>
       </c>
       <c r="B2" t="n">
-        <v>57818</v>
+        <v>79193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102999</v>
+        <v>1352</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568640</v>
+        <v>568809</v>
       </c>
       <c r="R2" t="n">
-        <v>6520370</v>
+        <v>6520479</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Högt upp på gren.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +776,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Asp.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122640499</v>
+        <v>122640518</v>
       </c>
       <c r="B3" t="n">
-        <v>79192</v>
+        <v>57819</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1352</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568809</v>
+        <v>568640</v>
       </c>
       <c r="R3" t="n">
-        <v>6520479</v>
+        <v>6520370</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Högt upp på gren.</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,11 +893,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Asp.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 38978-2023 artfynd.xlsx
+++ b/artfynd/A 38978-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122640499</v>
       </c>
       <c r="B2" t="n">
-        <v>79193</v>
+        <v>79196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 38978-2023 artfynd.xlsx
+++ b/artfynd/A 38978-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122640499</v>
       </c>
       <c r="B2" t="n">
-        <v>79196</v>
+        <v>79298</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>122640518</v>
       </c>
       <c r="B3" t="n">
-        <v>57819</v>
+        <v>57913</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 38978-2023 artfynd.xlsx
+++ b/artfynd/A 38978-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122640499</v>
+        <v>122640518</v>
       </c>
       <c r="B2" t="n">
-        <v>79298</v>
+        <v>57913</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1352</v>
+        <v>102999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568809</v>
+        <v>568640</v>
       </c>
       <c r="R2" t="n">
-        <v>6520479</v>
+        <v>6520370</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Högt upp på gren.</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,11 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Asp.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122640518</v>
+        <v>122640499</v>
       </c>
       <c r="B3" t="n">
-        <v>57913</v>
+        <v>79302</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>1352</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568640</v>
+        <v>568809</v>
       </c>
       <c r="R3" t="n">
-        <v>6520370</v>
+        <v>6520479</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Högt upp på gren.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +888,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Asp.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 38978-2023 artfynd.xlsx
+++ b/artfynd/A 38978-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122640518</v>
+        <v>122640499</v>
       </c>
       <c r="B2" t="n">
-        <v>57913</v>
+        <v>79302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102999</v>
+        <v>1352</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568640</v>
+        <v>568809</v>
       </c>
       <c r="R2" t="n">
-        <v>6520370</v>
+        <v>6520479</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Högt upp på gren.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +776,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Asp.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122640499</v>
+        <v>122640518</v>
       </c>
       <c r="B3" t="n">
-        <v>79302</v>
+        <v>57913</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1352</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568809</v>
+        <v>568640</v>
       </c>
       <c r="R3" t="n">
-        <v>6520479</v>
+        <v>6520370</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Högt upp på gren.</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,11 +893,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Asp.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 38978-2023 artfynd.xlsx
+++ b/artfynd/A 38978-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122640499</v>
+        <v>122640518</v>
       </c>
       <c r="B2" t="n">
-        <v>79302</v>
+        <v>57913</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1352</v>
+        <v>102999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568809</v>
+        <v>568640</v>
       </c>
       <c r="R2" t="n">
-        <v>6520479</v>
+        <v>6520370</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Högt upp på gren.</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,11 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Asp.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122640518</v>
+        <v>122640499</v>
       </c>
       <c r="B3" t="n">
-        <v>57913</v>
+        <v>79302</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>1352</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568640</v>
+        <v>568809</v>
       </c>
       <c r="R3" t="n">
-        <v>6520370</v>
+        <v>6520479</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Högt upp på gren.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +888,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Asp.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
